--- a/02_DIA_inicio_2026_analisis_assets/rbd_9704_escuela-lo-valledor_nt1_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9704_escuela-lo-valledor_nt1_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35738568-7EFE-4E0C-925B-DBCCB5F1DB20}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80046403-E2D1-4C54-9629-FF37A077423D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8761151-C054-4BEA-B4F1-6D225D1DBF6B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B48DDC5-E48D-41D3-B242-C55E84B249C7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED032932-3200-4452-8F42-4866A29831DC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFA482D0-7EB0-4E3D-92F5-C92FE2D9C691}"/>
 </file>